--- a/output/archive/Tarnovell_Group/Commercial/Cross_Sell/2026/Cross_Sell_White_Space_Matrix_DRAFT_v2.xlsx
+++ b/output/archive/Tarnovell_Group/Commercial/Cross_Sell/2026/Cross_Sell_White_Space_Matrix_DRAFT_v2.xlsx
@@ -442,7 +442,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -470,10 +470,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>'-' = never bought from this firm. Rows 9-14 still to be completed from the LIMS export.</t>
-        </is>
-      </c>
-    </row>
+          <t>'-' = no purchase recorded in reviewed A-F sources (CRM and LIMS exports to July 2026). Accounts 9-14 (worksheet rows 13-18) still to be completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1099,6 +1100,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -1107,10 +1109,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
@@ -1129,11 +1134,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>[TBC] owners for rows 9-14</t>
+          <t>[TBC] owners for accounts 9-14</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>